--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IC101"/>
+  <dimension ref="A1:IC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91054,6 +91054,3170 @@
       <c r="IB101" t="inlineStr"/>
       <c r="IC101" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>E7mOU6ff</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>iannarilli antony</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>4CQoUvoA</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>cancellotti tommaso</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>r7TIOlXj</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>armellino marco</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>t23s6fm4</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>frascatore paolo</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>CQBR5B92</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>d ausilio michele</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>YwwYfXn7</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>palmiero luca</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>KOKJAtq7</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>tribuzzi alessio</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>4pCR0JnU</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>rocca michele</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>CYq0fk4G</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>liotti daniele</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>KMmfYvvf</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>patierno cosimo</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>pEpm6Yvi</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>gori gabriele</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>MHIEnmbm</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>matosevic kristjan</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>4vpyISi8</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>floriani romano</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>fDBYqhcf</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>bellich marco</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>lYD8hHV2</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>varnier marco</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>Msnxdjh6</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>mignanelli daniele</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>APo2PW3H</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>buglio davide</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>OKLO0yfk</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>leone giuseppe</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>YwNkUuc0</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>pierobon christian</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>YTW7WSc7</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>romeo federico</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>KAVGuGeo</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>piscopo kevin</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>lbJUZPxb</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>artistico gabriele</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>jmK9pHmm</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>arzillo vincenzo</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>txZro8GK</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>benedetti simone</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>nwuJgSGk</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>cancellieri damiano</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>lt2qSjLr</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>de cristofaro antonio</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>jgqeZ2zA</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>fusco salvatore</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>6sSiUjMJ</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>guarnieri mattia</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>zibNnQ1D</t>
+        </is>
+      </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>llano manuel</t>
+        </is>
+      </c>
+      <c r="BH102" t="inlineStr">
+        <is>
+          <t>8OtkcXfh</t>
+        </is>
+      </c>
+      <c r="BI102" t="inlineStr">
+        <is>
+          <t>maisto francesco</t>
+        </is>
+      </c>
+      <c r="BJ102" t="inlineStr">
+        <is>
+          <t>trVxivFo</t>
+        </is>
+      </c>
+      <c r="BK102" t="inlineStr">
+        <is>
+          <t>marson leonardo</t>
+        </is>
+      </c>
+      <c r="BL102" t="inlineStr">
+        <is>
+          <t>8YIUQX6S</t>
+        </is>
+      </c>
+      <c r="BM102" t="inlineStr">
+        <is>
+          <t>rigione michele</t>
+        </is>
+      </c>
+      <c r="BN102" t="inlineStr">
+        <is>
+          <t>4rD2qMLm</t>
+        </is>
+      </c>
+      <c r="BO102" t="inlineStr">
+        <is>
+          <t>russo raffaele</t>
+        </is>
+      </c>
+      <c r="BP102" t="inlineStr">
+        <is>
+          <t>QFMylff9</t>
+        </is>
+      </c>
+      <c r="BQ102" t="inlineStr">
+        <is>
+          <t>andreoni cristian</t>
+        </is>
+      </c>
+      <c r="BR102" t="inlineStr">
+        <is>
+          <t>jRW1tUsI</t>
+        </is>
+      </c>
+      <c r="BS102" t="inlineStr">
+        <is>
+          <t>baldi matteo</t>
+        </is>
+      </c>
+      <c r="BT102" t="inlineStr">
+        <is>
+          <t>xCsi3lKT</t>
+        </is>
+      </c>
+      <c r="BU102" t="inlineStr">
+        <is>
+          <t>candellone leonardo</t>
+        </is>
+      </c>
+      <c r="BV102" t="inlineStr">
+        <is>
+          <t>rBgOPCjm</t>
+        </is>
+      </c>
+      <c r="BW102" t="inlineStr">
+        <is>
+          <t>da riva jacopo</t>
+        </is>
+      </c>
+      <c r="BX102" t="inlineStr">
+        <is>
+          <t>n7lX8IyB</t>
+        </is>
+      </c>
+      <c r="BY102" t="inlineStr">
+        <is>
+          <t>di dio flavio</t>
+        </is>
+      </c>
+      <c r="BZ102" t="inlineStr">
+        <is>
+          <t>KSk57mgG</t>
+        </is>
+      </c>
+      <c r="CA102" t="inlineStr">
+        <is>
+          <t>di marco tommaso</t>
+        </is>
+      </c>
+      <c r="CB102" t="inlineStr">
+        <is>
+          <t>bgM9MCsl</t>
+        </is>
+      </c>
+      <c r="CC102" t="inlineStr">
+        <is>
+          <t>esposito matteo</t>
+        </is>
+      </c>
+      <c r="CD102" t="inlineStr">
+        <is>
+          <t>ANCHAv7b</t>
+        </is>
+      </c>
+      <c r="CE102" t="inlineStr">
+        <is>
+          <t>folino francesco</t>
+        </is>
+      </c>
+      <c r="CF102" t="inlineStr">
+        <is>
+          <t>rLXzCfpN</t>
+        </is>
+      </c>
+      <c r="CG102" t="inlineStr">
+        <is>
+          <t>guarracino mariano</t>
+        </is>
+      </c>
+      <c r="CH102" t="inlineStr">
+        <is>
+          <t>xSoLBf8J</t>
+        </is>
+      </c>
+      <c r="CI102" t="inlineStr">
+        <is>
+          <t>meli marco</t>
+        </is>
+      </c>
+      <c r="CJ102" t="inlineStr">
+        <is>
+          <t>0fXqxXmN</t>
+        </is>
+      </c>
+      <c r="CK102" t="inlineStr">
+        <is>
+          <t>rocchetti yuri</t>
+        </is>
+      </c>
+      <c r="CL102" t="inlineStr">
+        <is>
+          <t>On46eNg0</t>
+        </is>
+      </c>
+      <c r="CM102" t="inlineStr">
+        <is>
+          <t>ruggero marco</t>
+        </is>
+      </c>
+      <c r="CN102" t="inlineStr">
+        <is>
+          <t>KUj8H9z1</t>
+        </is>
+      </c>
+      <c r="CO102" t="inlineStr">
+        <is>
+          <t>signorini alessandro</t>
+        </is>
+      </c>
+      <c r="CP102" t="inlineStr">
+        <is>
+          <t>4rD2qMLm</t>
+        </is>
+      </c>
+      <c r="CQ102" t="inlineStr">
+        <is>
+          <t>russo raffaele</t>
+        </is>
+      </c>
+      <c r="CR102" t="inlineStr">
+        <is>
+          <t>4rD2qMLm</t>
+        </is>
+      </c>
+      <c r="CS102" t="inlineStr">
+        <is>
+          <t>russo raffaele</t>
+        </is>
+      </c>
+      <c r="CT102" t="inlineStr">
+        <is>
+          <t>KMmfYvvf</t>
+        </is>
+      </c>
+      <c r="CU102" t="inlineStr">
+        <is>
+          <t>patierno cosimo</t>
+        </is>
+      </c>
+      <c r="CV102" t="inlineStr">
+        <is>
+          <t>lt2qSjLr</t>
+        </is>
+      </c>
+      <c r="CW102" t="inlineStr">
+        <is>
+          <t>de cristofaro antonio</t>
+        </is>
+      </c>
+      <c r="CX102" t="inlineStr">
+        <is>
+          <t>lt2qSjLr</t>
+        </is>
+      </c>
+      <c r="CY102" t="inlineStr">
+        <is>
+          <t>de cristofaro antonio</t>
+        </is>
+      </c>
+      <c r="CZ102" t="inlineStr">
+        <is>
+          <t>4pCR0JnU</t>
+        </is>
+      </c>
+      <c r="DA102" t="inlineStr">
+        <is>
+          <t>rocca michele</t>
+        </is>
+      </c>
+      <c r="DB102" t="inlineStr">
+        <is>
+          <t>UXbPSRqh</t>
+        </is>
+      </c>
+      <c r="DC102" t="inlineStr">
+        <is>
+          <t>sounas dimitris</t>
+        </is>
+      </c>
+      <c r="DD102" t="inlineStr">
+        <is>
+          <t>UXbPSRqh</t>
+        </is>
+      </c>
+      <c r="DE102" t="inlineStr">
+        <is>
+          <t>sounas dimitris</t>
+        </is>
+      </c>
+      <c r="DF102" t="inlineStr">
+        <is>
+          <t>CQBR5B92</t>
+        </is>
+      </c>
+      <c r="DG102" t="inlineStr">
+        <is>
+          <t>d ausilio michele</t>
+        </is>
+      </c>
+      <c r="DH102" t="inlineStr">
+        <is>
+          <t>xAvF8BUe</t>
+        </is>
+      </c>
+      <c r="DI102" t="inlineStr">
+        <is>
+          <t>vano michele</t>
+        </is>
+      </c>
+      <c r="DJ102" t="inlineStr">
+        <is>
+          <t>xAvF8BUe</t>
+        </is>
+      </c>
+      <c r="DK102" t="inlineStr">
+        <is>
+          <t>vano michele</t>
+        </is>
+      </c>
+      <c r="DL102" t="inlineStr">
+        <is>
+          <t>pEpm6Yvi</t>
+        </is>
+      </c>
+      <c r="DM102" t="inlineStr">
+        <is>
+          <t>gori gabriele</t>
+        </is>
+      </c>
+      <c r="DN102" t="inlineStr">
+        <is>
+          <t>nwuJgSGk</t>
+        </is>
+      </c>
+      <c r="DO102" t="inlineStr">
+        <is>
+          <t>cancellieri damiano</t>
+        </is>
+      </c>
+      <c r="DP102" t="inlineStr">
+        <is>
+          <t>nwuJgSGk</t>
+        </is>
+      </c>
+      <c r="DQ102" t="inlineStr">
+        <is>
+          <t>cancellieri damiano</t>
+        </is>
+      </c>
+      <c r="DR102" t="inlineStr">
+        <is>
+          <t>CYq0fk4G</t>
+        </is>
+      </c>
+      <c r="DS102" t="inlineStr">
+        <is>
+          <t>liotti daniele</t>
+        </is>
+      </c>
+      <c r="DT102" t="inlineStr">
+        <is>
+          <t>KSk57mgG</t>
+        </is>
+      </c>
+      <c r="DU102" t="inlineStr">
+        <is>
+          <t>di marco tommaso</t>
+        </is>
+      </c>
+      <c r="DV102" t="inlineStr">
+        <is>
+          <t>KSk57mgG</t>
+        </is>
+      </c>
+      <c r="DW102" t="inlineStr">
+        <is>
+          <t>di marco tommaso</t>
+        </is>
+      </c>
+      <c r="DX102" t="inlineStr">
+        <is>
+          <t>YTW7WSc7</t>
+        </is>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>romeo federico</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>4YPLcYRF</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr">
+        <is>
+          <t>tonin riccardo</t>
+        </is>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>4YPLcYRF</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr">
+        <is>
+          <t>tonin riccardo</t>
+        </is>
+      </c>
+      <c r="ED102" t="inlineStr">
+        <is>
+          <t>YwNkUuc0</t>
+        </is>
+      </c>
+      <c r="EE102" t="inlineStr">
+        <is>
+          <t>pierobon christian</t>
+        </is>
+      </c>
+      <c r="EF102" t="inlineStr">
+        <is>
+          <t>0fXqxXmN</t>
+        </is>
+      </c>
+      <c r="EG102" t="inlineStr">
+        <is>
+          <t>rocchetti yuri</t>
+        </is>
+      </c>
+      <c r="EH102" t="inlineStr">
+        <is>
+          <t>0fXqxXmN</t>
+        </is>
+      </c>
+      <c r="EI102" t="inlineStr">
+        <is>
+          <t>rocchetti yuri</t>
+        </is>
+      </c>
+      <c r="EJ102" t="inlineStr">
+        <is>
+          <t>Msnxdjh6</t>
+        </is>
+      </c>
+      <c r="EK102" t="inlineStr">
+        <is>
+          <t>mignanelli daniele</t>
+        </is>
+      </c>
+      <c r="EL102" t="inlineStr">
+        <is>
+          <t>xCsi3lKT</t>
+        </is>
+      </c>
+      <c r="EM102" t="inlineStr">
+        <is>
+          <t>candellone leonardo</t>
+        </is>
+      </c>
+      <c r="EN102" t="inlineStr">
+        <is>
+          <t>xCsi3lKT</t>
+        </is>
+      </c>
+      <c r="EO102" t="inlineStr">
+        <is>
+          <t>candellone leonardo</t>
+        </is>
+      </c>
+      <c r="EP102" t="inlineStr">
+        <is>
+          <t>OKLO0yfk</t>
+        </is>
+      </c>
+      <c r="EQ102" t="inlineStr">
+        <is>
+          <t>leone giuseppe</t>
+        </is>
+      </c>
+      <c r="ER102" t="inlineStr">
+        <is>
+          <t>On46eNg0</t>
+        </is>
+      </c>
+      <c r="ES102" t="inlineStr">
+        <is>
+          <t>ruggero marco</t>
+        </is>
+      </c>
+      <c r="ET102" t="inlineStr">
+        <is>
+          <t>On46eNg0</t>
+        </is>
+      </c>
+      <c r="EU102" t="inlineStr">
+        <is>
+          <t>ruggero marco</t>
+        </is>
+      </c>
+      <c r="EV102" t="inlineStr">
+        <is>
+          <t>lYD8hHV2</t>
+        </is>
+      </c>
+      <c r="EW102" t="inlineStr">
+        <is>
+          <t>varnier marco</t>
+        </is>
+      </c>
+      <c r="EX102" t="inlineStr"/>
+      <c r="EY102" t="inlineStr"/>
+      <c r="EZ102" t="inlineStr"/>
+      <c r="FA102" t="inlineStr"/>
+      <c r="FB102" t="inlineStr"/>
+      <c r="FC102" t="inlineStr"/>
+      <c r="FD102" t="inlineStr"/>
+      <c r="FE102" t="inlineStr"/>
+      <c r="FF102" t="inlineStr">
+        <is>
+          <t>EZN6Bu3i</t>
+        </is>
+      </c>
+      <c r="FG102" t="inlineStr">
+        <is>
+          <t>sannipoli daniel</t>
+        </is>
+      </c>
+      <c r="FH102" t="inlineStr">
+        <is>
+          <t>UXbPSRqh</t>
+        </is>
+      </c>
+      <c r="FI102" t="inlineStr">
+        <is>
+          <t>sounas dimitris</t>
+        </is>
+      </c>
+      <c r="FJ102" t="inlineStr">
+        <is>
+          <t>4YPLcYRF</t>
+        </is>
+      </c>
+      <c r="FK102" t="inlineStr">
+        <is>
+          <t>tonin riccardo</t>
+        </is>
+      </c>
+      <c r="FL102" t="inlineStr"/>
+      <c r="FM102" t="inlineStr"/>
+      <c r="FN102" t="inlineStr"/>
+      <c r="FO102" t="inlineStr"/>
+      <c r="FP102" t="inlineStr">
+        <is>
+          <t>YLLycp6S</t>
+        </is>
+      </c>
+      <c r="FQ102" t="inlineStr">
+        <is>
+          <t>toscano marco</t>
+        </is>
+      </c>
+      <c r="FR102" t="inlineStr">
+        <is>
+          <t>xAvF8BUe</t>
+        </is>
+      </c>
+      <c r="FS102" t="inlineStr">
+        <is>
+          <t>vano michele</t>
+        </is>
+      </c>
+      <c r="FT102" t="inlineStr"/>
+      <c r="FU102" t="inlineStr"/>
+      <c r="FV102" t="inlineStr"/>
+      <c r="FW102" t="inlineStr"/>
+      <c r="FX102" t="inlineStr"/>
+      <c r="FY102" t="inlineStr"/>
+      <c r="FZ102" t="inlineStr"/>
+      <c r="GA102" t="inlineStr"/>
+      <c r="GB102" t="inlineStr"/>
+      <c r="GC102" t="inlineStr"/>
+      <c r="GD102" t="inlineStr"/>
+      <c r="GE102" t="inlineStr"/>
+      <c r="GF102" t="inlineStr"/>
+      <c r="GG102" t="inlineStr"/>
+      <c r="GH102" t="inlineStr"/>
+      <c r="GI102" t="inlineStr"/>
+      <c r="GJ102" t="inlineStr"/>
+      <c r="GK102" t="inlineStr"/>
+      <c r="GL102" t="inlineStr"/>
+      <c r="GM102" t="inlineStr"/>
+      <c r="GN102" t="inlineStr"/>
+      <c r="GO102" t="inlineStr"/>
+      <c r="GP102" t="inlineStr"/>
+      <c r="GQ102" t="inlineStr"/>
+      <c r="GR102" t="inlineStr"/>
+      <c r="GS102" t="inlineStr"/>
+      <c r="GT102" t="inlineStr"/>
+      <c r="GU102" t="inlineStr"/>
+      <c r="GV102" t="inlineStr"/>
+      <c r="GW102" t="inlineStr"/>
+      <c r="GX102" t="inlineStr"/>
+      <c r="GY102" t="inlineStr"/>
+      <c r="GZ102" t="inlineStr"/>
+      <c r="HA102" t="inlineStr"/>
+      <c r="HB102" t="inlineStr"/>
+      <c r="HC102" t="inlineStr"/>
+      <c r="HD102" t="inlineStr"/>
+      <c r="HE102" t="inlineStr"/>
+      <c r="HF102" t="inlineStr"/>
+      <c r="HG102" t="inlineStr"/>
+      <c r="HH102" t="inlineStr"/>
+      <c r="HI102" t="inlineStr"/>
+      <c r="HJ102" t="inlineStr"/>
+      <c r="HK102" t="inlineStr"/>
+      <c r="HL102" t="inlineStr"/>
+      <c r="HM102" t="inlineStr"/>
+      <c r="HN102" t="inlineStr"/>
+      <c r="HO102" t="inlineStr"/>
+      <c r="HP102" t="inlineStr"/>
+      <c r="HQ102" t="inlineStr"/>
+      <c r="HR102" t="inlineStr"/>
+      <c r="HS102" t="inlineStr"/>
+      <c r="HT102" t="inlineStr"/>
+      <c r="HU102" t="inlineStr"/>
+      <c r="HV102" t="inlineStr"/>
+      <c r="HW102" t="inlineStr"/>
+      <c r="HX102" t="inlineStr"/>
+      <c r="HY102" t="inlineStr"/>
+      <c r="HZ102" t="inlineStr"/>
+      <c r="IA102" t="inlineStr"/>
+      <c r="IB102" t="inlineStr"/>
+      <c r="IC102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>tlSr8Yco</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>pisseri matteo</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2qAN5836</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>adamo emanuele</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>n7piqBuG</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>bastoni simone</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>hjLa97a7</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>berti tommaso</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>pnI8ZjZr</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ceesay joseph</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>xIKq8Lhb</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>curto marco</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>tnsZtqGu</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>donnarumma daniele</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>WrbFYwR8</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>kargbo augustus</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>EBw91VL5</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>mangraviti massimiliano</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>fNkZk3Qs</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>prestia giuseppe</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>4MMcPxki</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>shpendi cristian</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>dQ4lpfUn</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>fortin mattia</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>nFntTiFE</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>capelli alessandro</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>ddBup58s</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>crisetig lorenzo</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>QiKjTfpa</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>delli carri filippo</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>fq15AKxo</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>faedo carlo</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>nurhgzqk</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>kirwan niko</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>MRTlac3k</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>palombi simone</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>2eYcJT8o</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>perrotta marco</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>YVWxIj3C</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>spagnoli alberto</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>v5LBKpgG</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>varas kevin</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>nkTmhR57</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>villa luca</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>ADBJ4OrH</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>antonucci mirko</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>OQAZiTD2</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>chiarello riccardo</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>2k9zUaAa</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>ciofi andrea</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>fiJmaURn</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>coveri valentino</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>hrgu7eZM</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>francesconi matteo</t>
+        </is>
+      </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>dG0Lm68C</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>klinsmann jonathan</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>GtGjeC0b</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>manetti giulio</t>
+        </is>
+      </c>
+      <c r="BH103" t="inlineStr">
+        <is>
+          <t>Me57xewm</t>
+        </is>
+      </c>
+      <c r="BI103" t="inlineStr">
+        <is>
+          <t>ogunseye roberto</t>
+        </is>
+      </c>
+      <c r="BJ103" t="inlineStr">
+        <is>
+          <t>2J6W9OsT</t>
+        </is>
+      </c>
+      <c r="BK103" t="inlineStr">
+        <is>
+          <t>piacentini matteo</t>
+        </is>
+      </c>
+      <c r="BL103" t="inlineStr">
+        <is>
+          <t>8CpA5o79</t>
+        </is>
+      </c>
+      <c r="BM103" t="inlineStr">
+        <is>
+          <t>pieraccini simone</t>
+        </is>
+      </c>
+      <c r="BN103" t="inlineStr">
+        <is>
+          <t>f3XNY1b3</t>
+        </is>
+      </c>
+      <c r="BO103" t="inlineStr">
+        <is>
+          <t>veliaj giulio</t>
+        </is>
+      </c>
+      <c r="BP103" t="inlineStr">
+        <is>
+          <t>67jItSNM</t>
+        </is>
+      </c>
+      <c r="BQ103" t="inlineStr">
+        <is>
+          <t>beccaro andrea</t>
+        </is>
+      </c>
+      <c r="BR103" t="inlineStr">
+        <is>
+          <t>dltgVpc5</t>
+        </is>
+      </c>
+      <c r="BS103" t="inlineStr">
+        <is>
+          <t>belli francesco</t>
+        </is>
+      </c>
+      <c r="BT103" t="inlineStr">
+        <is>
+          <t>t6PwGPus</t>
+        </is>
+      </c>
+      <c r="BU103" t="inlineStr">
+        <is>
+          <t>bianchi nicolo</t>
+        </is>
+      </c>
+      <c r="BV103" t="inlineStr">
+        <is>
+          <t>8dHdXK65</t>
+        </is>
+      </c>
+      <c r="BW103" t="inlineStr">
+        <is>
+          <t>bortolussi mattia</t>
+        </is>
+      </c>
+      <c r="BX103" t="inlineStr">
+        <is>
+          <t>nDfczDjl</t>
+        </is>
+      </c>
+      <c r="BY103" t="inlineStr">
+        <is>
+          <t>carniello matteo</t>
+        </is>
+      </c>
+      <c r="BZ103" t="inlineStr">
+        <is>
+          <t>r9YFBYWt</t>
+        </is>
+      </c>
+      <c r="CA103" t="inlineStr">
+        <is>
+          <t>crescenzi luca</t>
+        </is>
+      </c>
+      <c r="CB103" t="inlineStr">
+        <is>
+          <t>rmNUe7gb</t>
+        </is>
+      </c>
+      <c r="CC103" t="inlineStr">
+        <is>
+          <t>favale giulio</t>
+        </is>
+      </c>
+      <c r="CD103" t="inlineStr">
+        <is>
+          <t>2g5E1Wnl</t>
+        </is>
+      </c>
+      <c r="CE103" t="inlineStr">
+        <is>
+          <t>fusi pietro</t>
+        </is>
+      </c>
+      <c r="CF103" t="inlineStr">
+        <is>
+          <t>Crkmzfil</t>
+        </is>
+      </c>
+      <c r="CG103" t="inlineStr">
+        <is>
+          <t>granata antonio</t>
+        </is>
+      </c>
+      <c r="CH103" t="inlineStr">
+        <is>
+          <t>C6lg5MV5</t>
+        </is>
+      </c>
+      <c r="CI103" t="inlineStr">
+        <is>
+          <t>montrone andrea</t>
+        </is>
+      </c>
+      <c r="CJ103" t="inlineStr">
+        <is>
+          <t>bgpTQbF8</t>
+        </is>
+      </c>
+      <c r="CK103" t="inlineStr">
+        <is>
+          <t>russini simone</t>
+        </is>
+      </c>
+      <c r="CL103" t="inlineStr">
+        <is>
+          <t>dxkiamNH</t>
+        </is>
+      </c>
+      <c r="CM103" t="inlineStr">
+        <is>
+          <t>targa alberto</t>
+        </is>
+      </c>
+      <c r="CN103" t="inlineStr">
+        <is>
+          <t>ChodUzA7</t>
+        </is>
+      </c>
+      <c r="CO103" t="inlineStr">
+        <is>
+          <t>tumiatti francesco</t>
+        </is>
+      </c>
+      <c r="CP103" t="inlineStr"/>
+      <c r="CQ103" t="inlineStr"/>
+      <c r="CR103" t="inlineStr"/>
+      <c r="CS103" t="inlineStr"/>
+      <c r="CT103" t="inlineStr"/>
+      <c r="CU103" t="inlineStr"/>
+      <c r="CV103" t="inlineStr"/>
+      <c r="CW103" t="inlineStr"/>
+      <c r="CX103" t="inlineStr"/>
+      <c r="CY103" t="inlineStr"/>
+      <c r="CZ103" t="inlineStr"/>
+      <c r="DA103" t="inlineStr"/>
+      <c r="DB103" t="inlineStr"/>
+      <c r="DC103" t="inlineStr"/>
+      <c r="DD103" t="inlineStr"/>
+      <c r="DE103" t="inlineStr"/>
+      <c r="DF103" t="inlineStr"/>
+      <c r="DG103" t="inlineStr"/>
+      <c r="DH103" t="inlineStr"/>
+      <c r="DI103" t="inlineStr"/>
+      <c r="DJ103" t="inlineStr"/>
+      <c r="DK103" t="inlineStr"/>
+      <c r="DL103" t="inlineStr"/>
+      <c r="DM103" t="inlineStr"/>
+      <c r="DN103" t="inlineStr"/>
+      <c r="DO103" t="inlineStr"/>
+      <c r="DP103" t="inlineStr"/>
+      <c r="DQ103" t="inlineStr"/>
+      <c r="DR103" t="inlineStr"/>
+      <c r="DS103" t="inlineStr"/>
+      <c r="DT103" t="inlineStr"/>
+      <c r="DU103" t="inlineStr"/>
+      <c r="DV103" t="inlineStr"/>
+      <c r="DW103" t="inlineStr"/>
+      <c r="DX103" t="inlineStr"/>
+      <c r="DY103" t="inlineStr"/>
+      <c r="DZ103" t="inlineStr"/>
+      <c r="EA103" t="inlineStr"/>
+      <c r="EB103" t="inlineStr"/>
+      <c r="EC103" t="inlineStr"/>
+      <c r="ED103" t="inlineStr"/>
+      <c r="EE103" t="inlineStr"/>
+      <c r="EF103" t="inlineStr"/>
+      <c r="EG103" t="inlineStr"/>
+      <c r="EH103" t="inlineStr"/>
+      <c r="EI103" t="inlineStr"/>
+      <c r="EJ103" t="inlineStr"/>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+      <c r="EM103" t="inlineStr"/>
+      <c r="EN103" t="inlineStr"/>
+      <c r="EO103" t="inlineStr"/>
+      <c r="EP103" t="inlineStr"/>
+      <c r="EQ103" t="inlineStr"/>
+      <c r="ER103" t="inlineStr"/>
+      <c r="ES103" t="inlineStr"/>
+      <c r="ET103" t="inlineStr"/>
+      <c r="EU103" t="inlineStr"/>
+      <c r="EV103" t="inlineStr"/>
+      <c r="EW103" t="inlineStr"/>
+      <c r="EX103" t="inlineStr"/>
+      <c r="EY103" t="inlineStr"/>
+      <c r="EZ103" t="inlineStr"/>
+      <c r="FA103" t="inlineStr"/>
+      <c r="FB103" t="inlineStr"/>
+      <c r="FC103" t="inlineStr"/>
+      <c r="FD103" t="inlineStr"/>
+      <c r="FE103" t="inlineStr"/>
+      <c r="FF103" t="inlineStr"/>
+      <c r="FG103" t="inlineStr"/>
+      <c r="FH103" t="inlineStr"/>
+      <c r="FI103" t="inlineStr"/>
+      <c r="FJ103" t="inlineStr">
+        <is>
+          <t>EH92rx34</t>
+        </is>
+      </c>
+      <c r="FK103" t="inlineStr">
+        <is>
+          <t>voltan michele</t>
+        </is>
+      </c>
+      <c r="FL103" t="inlineStr"/>
+      <c r="FM103" t="inlineStr"/>
+      <c r="FN103" t="inlineStr"/>
+      <c r="FO103" t="inlineStr"/>
+      <c r="FP103" t="inlineStr"/>
+      <c r="FQ103" t="inlineStr"/>
+      <c r="FR103" t="inlineStr"/>
+      <c r="FS103" t="inlineStr"/>
+      <c r="FT103" t="inlineStr"/>
+      <c r="FU103" t="inlineStr"/>
+      <c r="FV103" t="inlineStr"/>
+      <c r="FW103" t="inlineStr"/>
+      <c r="FX103" t="inlineStr"/>
+      <c r="FY103" t="inlineStr"/>
+      <c r="FZ103" t="inlineStr"/>
+      <c r="GA103" t="inlineStr"/>
+      <c r="GB103" t="inlineStr"/>
+      <c r="GC103" t="inlineStr"/>
+      <c r="GD103" t="inlineStr"/>
+      <c r="GE103" t="inlineStr"/>
+      <c r="GF103" t="inlineStr"/>
+      <c r="GG103" t="inlineStr"/>
+      <c r="GH103" t="inlineStr"/>
+      <c r="GI103" t="inlineStr"/>
+      <c r="GJ103" t="inlineStr"/>
+      <c r="GK103" t="inlineStr"/>
+      <c r="GL103" t="inlineStr"/>
+      <c r="GM103" t="inlineStr"/>
+      <c r="GN103" t="inlineStr"/>
+      <c r="GO103" t="inlineStr"/>
+      <c r="GP103" t="inlineStr"/>
+      <c r="GQ103" t="inlineStr"/>
+      <c r="GR103" t="inlineStr"/>
+      <c r="GS103" t="inlineStr"/>
+      <c r="GT103" t="inlineStr"/>
+      <c r="GU103" t="inlineStr"/>
+      <c r="GV103" t="inlineStr"/>
+      <c r="GW103" t="inlineStr"/>
+      <c r="GX103" t="inlineStr"/>
+      <c r="GY103" t="inlineStr"/>
+      <c r="GZ103" t="inlineStr"/>
+      <c r="HA103" t="inlineStr"/>
+      <c r="HB103" t="inlineStr"/>
+      <c r="HC103" t="inlineStr"/>
+      <c r="HD103" t="inlineStr"/>
+      <c r="HE103" t="inlineStr"/>
+      <c r="HF103" t="inlineStr"/>
+      <c r="HG103" t="inlineStr"/>
+      <c r="HH103" t="inlineStr"/>
+      <c r="HI103" t="inlineStr"/>
+      <c r="HJ103" t="inlineStr"/>
+      <c r="HK103" t="inlineStr"/>
+      <c r="HL103" t="inlineStr"/>
+      <c r="HM103" t="inlineStr"/>
+      <c r="HN103" t="inlineStr"/>
+      <c r="HO103" t="inlineStr"/>
+      <c r="HP103" t="inlineStr"/>
+      <c r="HQ103" t="inlineStr"/>
+      <c r="HR103" t="inlineStr"/>
+      <c r="HS103" t="inlineStr"/>
+      <c r="HT103" t="inlineStr"/>
+      <c r="HU103" t="inlineStr"/>
+      <c r="HV103" t="inlineStr"/>
+      <c r="HW103" t="inlineStr"/>
+      <c r="HX103" t="inlineStr"/>
+      <c r="HY103" t="inlineStr"/>
+      <c r="HZ103" t="inlineStr"/>
+      <c r="IA103" t="inlineStr"/>
+      <c r="IB103" t="inlineStr"/>
+      <c r="IC103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SEov10r3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>zaccagno andrea</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wl8yLNw6</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>dametto paolo</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0GL6rwvR</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>antonelli nicolo</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>8z01NCGn</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>fabriani christian</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>WpHvq7xP</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>zecca giacomo</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Qm1pJ18I</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>giorico daniele</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>SfaKKxI4</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>brentan michael</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>KOJqQFFl</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>liviero matteo</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Y1ts5NY4</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>varela djamanca muhamed</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>d0Am5FU2</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>scotto luigi</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>v9XkZiaP</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>fischnaller manuel</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>ppkkwoIq</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>festa marco</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>dj7ewEp6</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>maggioni tommaso</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>rqTURYfL</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>redolfi alex</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>ngBZLdIk</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>brignani fabrizio</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>jLhOHa57</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>panizzi erik</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>I1MCXHlA</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>wieser david</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>ERIznhBT</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>burrai salvatore</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>dfLh9Nso</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>trimboli simone</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>r96jf7K7</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>mancuso leonardo</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>8rHEthHl</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>fiori antonio</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>SULw1d9h</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>galuppini francesco</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>AkVabcvj</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>coccolo luca</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>A3xoHdtI</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>diakite adama</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>KpgeUmOi</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>goglino patricio</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>WIzgR6Y5</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>guiebre abdoul</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>pYKJzfur</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>idda riccardo</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>b1hJOUZq</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>masala alessandro</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>QFW8Bw7T</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>mastinu giuseppe</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>lfWXYzys</t>
+        </is>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>nunziatini francesco</t>
+        </is>
+      </c>
+      <c r="BJ104" t="inlineStr">
+        <is>
+          <t>GQ1SLUeH</t>
+        </is>
+      </c>
+      <c r="BK104" t="inlineStr">
+        <is>
+          <t>petriccione danilo</t>
+        </is>
+      </c>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>42GAqfug</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr">
+        <is>
+          <t>cristian petricciuolo</t>
+        </is>
+      </c>
+      <c r="BN104" t="inlineStr">
+        <is>
+          <t>8U29ARK7</t>
+        </is>
+      </c>
+      <c r="BO104" t="inlineStr">
+        <is>
+          <t>sanat ayman</t>
+        </is>
+      </c>
+      <c r="BP104" t="inlineStr">
+        <is>
+          <t>CxdWXum0</t>
+        </is>
+      </c>
+      <c r="BQ104" t="inlineStr">
+        <is>
+          <t>aramu mattia</t>
+        </is>
+      </c>
+      <c r="BR104" t="inlineStr">
+        <is>
+          <t>SzgxNIFd</t>
+        </is>
+      </c>
+      <c r="BS104" t="inlineStr">
+        <is>
+          <t>artioli federico</t>
+        </is>
+      </c>
+      <c r="BT104" t="inlineStr">
+        <is>
+          <t>nFKFHQYJ</t>
+        </is>
+      </c>
+      <c r="BU104" t="inlineStr">
+        <is>
+          <t>bani cristiano</t>
+        </is>
+      </c>
+      <c r="BV104" t="inlineStr">
+        <is>
+          <t>jmAOtCAB</t>
+        </is>
+      </c>
+      <c r="BW104" t="inlineStr">
+        <is>
+          <t>botti federico</t>
+        </is>
+      </c>
+      <c r="BX104" t="inlineStr">
+        <is>
+          <t>ULHzNvxG</t>
+        </is>
+      </c>
+      <c r="BY104" t="inlineStr">
+        <is>
+          <t>bragantini davide</t>
+        </is>
+      </c>
+      <c r="BZ104" t="inlineStr">
+        <is>
+          <t>v1cJQRlH</t>
+        </is>
+      </c>
+      <c r="CA104" t="inlineStr">
+        <is>
+          <t>cella stefano</t>
+        </is>
+      </c>
+      <c r="CB104" t="inlineStr">
+        <is>
+          <t>zabBo8TD</t>
+        </is>
+      </c>
+      <c r="CC104" t="inlineStr">
+        <is>
+          <t>debenedetti alessandro</t>
+        </is>
+      </c>
+      <c r="CD104" t="inlineStr">
+        <is>
+          <t>vwQdsuRJ</t>
+        </is>
+      </c>
+      <c r="CE104" t="inlineStr">
+        <is>
+          <t>de maio sebastian</t>
+        </is>
+      </c>
+      <c r="CF104" t="inlineStr">
+        <is>
+          <t>rLXjAPEC</t>
+        </is>
+      </c>
+      <c r="CG104" t="inlineStr">
+        <is>
+          <t>fedel giacomo</t>
+        </is>
+      </c>
+      <c r="CH104" t="inlineStr">
+        <is>
+          <t>llxIMxss</t>
+        </is>
+      </c>
+      <c r="CI104" t="inlineStr">
+        <is>
+          <t>mensah davis</t>
+        </is>
+      </c>
+      <c r="CJ104" t="inlineStr">
+        <is>
+          <t>nPDWBMl9</t>
+        </is>
+      </c>
+      <c r="CK104" t="inlineStr">
+        <is>
+          <t>muroni mattia</t>
+        </is>
+      </c>
+      <c r="CL104" t="inlineStr">
+        <is>
+          <t>S6rP7VQf</t>
+        </is>
+      </c>
+      <c r="CM104" t="inlineStr">
+        <is>
+          <t>radaelli nicolo</t>
+        </is>
+      </c>
+      <c r="CN104" t="inlineStr">
+        <is>
+          <t>dCTZFBZK</t>
+        </is>
+      </c>
+      <c r="CO104" t="inlineStr">
+        <is>
+          <t>ruocco francesco</t>
+        </is>
+      </c>
+      <c r="CP104" t="inlineStr">
+        <is>
+          <t>WIzgR6Y5</t>
+        </is>
+      </c>
+      <c r="CQ104" t="inlineStr">
+        <is>
+          <t>guiebre abdoul</t>
+        </is>
+      </c>
+      <c r="CR104" t="inlineStr">
+        <is>
+          <t>WIzgR6Y5</t>
+        </is>
+      </c>
+      <c r="CS104" t="inlineStr">
+        <is>
+          <t>guiebre abdoul</t>
+        </is>
+      </c>
+      <c r="CT104" t="inlineStr">
+        <is>
+          <t>KOJqQFFl</t>
+        </is>
+      </c>
+      <c r="CU104" t="inlineStr">
+        <is>
+          <t>liviero matteo</t>
+        </is>
+      </c>
+      <c r="CV104" t="inlineStr">
+        <is>
+          <t>QFW8Bw7T</t>
+        </is>
+      </c>
+      <c r="CW104" t="inlineStr">
+        <is>
+          <t>mastinu giuseppe</t>
+        </is>
+      </c>
+      <c r="CX104" t="inlineStr">
+        <is>
+          <t>QFW8Bw7T</t>
+        </is>
+      </c>
+      <c r="CY104" t="inlineStr">
+        <is>
+          <t>mastinu giuseppe</t>
+        </is>
+      </c>
+      <c r="CZ104" t="inlineStr">
+        <is>
+          <t>d0Am5FU2</t>
+        </is>
+      </c>
+      <c r="DA104" t="inlineStr">
+        <is>
+          <t>scotto luigi</t>
+        </is>
+      </c>
+      <c r="DB104" t="inlineStr">
+        <is>
+          <t>KpgeUmOi</t>
+        </is>
+      </c>
+      <c r="DC104" t="inlineStr">
+        <is>
+          <t>goglino patricio</t>
+        </is>
+      </c>
+      <c r="DD104" t="inlineStr">
+        <is>
+          <t>KpgeUmOi</t>
+        </is>
+      </c>
+      <c r="DE104" t="inlineStr">
+        <is>
+          <t>goglino patricio</t>
+        </is>
+      </c>
+      <c r="DF104" t="inlineStr">
+        <is>
+          <t>SfaKKxI4</t>
+        </is>
+      </c>
+      <c r="DG104" t="inlineStr">
+        <is>
+          <t>brentan michael</t>
+        </is>
+      </c>
+      <c r="DH104" t="inlineStr">
+        <is>
+          <t>A3xoHdtI</t>
+        </is>
+      </c>
+      <c r="DI104" t="inlineStr">
+        <is>
+          <t>diakite adama</t>
+        </is>
+      </c>
+      <c r="DJ104" t="inlineStr">
+        <is>
+          <t>A3xoHdtI</t>
+        </is>
+      </c>
+      <c r="DK104" t="inlineStr">
+        <is>
+          <t>diakite adama</t>
+        </is>
+      </c>
+      <c r="DL104" t="inlineStr">
+        <is>
+          <t>v9XkZiaP</t>
+        </is>
+      </c>
+      <c r="DM104" t="inlineStr">
+        <is>
+          <t>fischnaller manuel</t>
+        </is>
+      </c>
+      <c r="DN104" t="inlineStr">
+        <is>
+          <t>QLwfj68R</t>
+        </is>
+      </c>
+      <c r="DO104" t="inlineStr">
+        <is>
+          <t>zambataro eyob</t>
+        </is>
+      </c>
+      <c r="DP104" t="inlineStr">
+        <is>
+          <t>QLwfj68R</t>
+        </is>
+      </c>
+      <c r="DQ104" t="inlineStr">
+        <is>
+          <t>zambataro eyob</t>
+        </is>
+      </c>
+      <c r="DR104" t="inlineStr">
+        <is>
+          <t>WpHvq7xP</t>
+        </is>
+      </c>
+      <c r="DS104" t="inlineStr">
+        <is>
+          <t>zecca giacomo</t>
+        </is>
+      </c>
+      <c r="DT104" t="inlineStr">
+        <is>
+          <t>ULHzNvxG</t>
+        </is>
+      </c>
+      <c r="DU104" t="inlineStr">
+        <is>
+          <t>bragantini davide</t>
+        </is>
+      </c>
+      <c r="DV104" t="inlineStr">
+        <is>
+          <t>ULHzNvxG</t>
+        </is>
+      </c>
+      <c r="DW104" t="inlineStr">
+        <is>
+          <t>bragantini davide</t>
+        </is>
+      </c>
+      <c r="DX104" t="inlineStr">
+        <is>
+          <t>8rHEthHl</t>
+        </is>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>fiori antonio</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>dCTZFBZK</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>ruocco francesco</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>dCTZFBZK</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr">
+        <is>
+          <t>ruocco francesco</t>
+        </is>
+      </c>
+      <c r="ED104" t="inlineStr">
+        <is>
+          <t>SULw1d9h</t>
+        </is>
+      </c>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>galuppini francesco</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>llxIMxss</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>mensah davis</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>llxIMxss</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>mensah davis</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>r96jf7K7</t>
+        </is>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>mancuso leonardo</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr">
+        <is>
+          <t>CxdWXum0</t>
+        </is>
+      </c>
+      <c r="EM104" t="inlineStr">
+        <is>
+          <t>aramu mattia</t>
+        </is>
+      </c>
+      <c r="EN104" t="inlineStr">
+        <is>
+          <t>CxdWXum0</t>
+        </is>
+      </c>
+      <c r="EO104" t="inlineStr">
+        <is>
+          <t>aramu mattia</t>
+        </is>
+      </c>
+      <c r="EP104" t="inlineStr">
+        <is>
+          <t>I1MCXHlA</t>
+        </is>
+      </c>
+      <c r="EQ104" t="inlineStr">
+        <is>
+          <t>wieser david</t>
+        </is>
+      </c>
+      <c r="ER104" t="inlineStr">
+        <is>
+          <t>nPDWBMl9</t>
+        </is>
+      </c>
+      <c r="ES104" t="inlineStr">
+        <is>
+          <t>muroni mattia</t>
+        </is>
+      </c>
+      <c r="ET104" t="inlineStr">
+        <is>
+          <t>nPDWBMl9</t>
+        </is>
+      </c>
+      <c r="EU104" t="inlineStr">
+        <is>
+          <t>muroni mattia</t>
+        </is>
+      </c>
+      <c r="EV104" t="inlineStr">
+        <is>
+          <t>dfLh9Nso</t>
+        </is>
+      </c>
+      <c r="EW104" t="inlineStr">
+        <is>
+          <t>trimboli simone</t>
+        </is>
+      </c>
+      <c r="EX104" t="inlineStr"/>
+      <c r="EY104" t="inlineStr"/>
+      <c r="EZ104" t="inlineStr"/>
+      <c r="FA104" t="inlineStr"/>
+      <c r="FB104" t="inlineStr"/>
+      <c r="FC104" t="inlineStr"/>
+      <c r="FD104" t="inlineStr"/>
+      <c r="FE104" t="inlineStr"/>
+      <c r="FF104" t="inlineStr">
+        <is>
+          <t>hfQjJSLU</t>
+        </is>
+      </c>
+      <c r="FG104" t="inlineStr">
+        <is>
+          <t>verduci giuseppe</t>
+        </is>
+      </c>
+      <c r="FH104" t="inlineStr">
+        <is>
+          <t>QLwfj68R</t>
+        </is>
+      </c>
+      <c r="FI104" t="inlineStr">
+        <is>
+          <t>zambataro eyob</t>
+        </is>
+      </c>
+      <c r="FJ104" t="inlineStr">
+        <is>
+          <t>jqRz1ZBa</t>
+        </is>
+      </c>
+      <c r="FK104" t="inlineStr">
+        <is>
+          <t>solini matteo</t>
+        </is>
+      </c>
+      <c r="FL104" t="inlineStr"/>
+      <c r="FM104" t="inlineStr"/>
+      <c r="FN104" t="inlineStr"/>
+      <c r="FO104" t="inlineStr"/>
+      <c r="FP104" t="inlineStr"/>
+      <c r="FQ104" t="inlineStr"/>
+      <c r="FR104" t="inlineStr"/>
+      <c r="FS104" t="inlineStr"/>
+      <c r="FT104" t="inlineStr"/>
+      <c r="FU104" t="inlineStr"/>
+      <c r="FV104" t="inlineStr"/>
+      <c r="FW104" t="inlineStr"/>
+      <c r="FX104" t="inlineStr"/>
+      <c r="FY104" t="inlineStr"/>
+      <c r="FZ104" t="inlineStr"/>
+      <c r="GA104" t="inlineStr"/>
+      <c r="GB104" t="inlineStr"/>
+      <c r="GC104" t="inlineStr"/>
+      <c r="GD104" t="inlineStr"/>
+      <c r="GE104" t="inlineStr"/>
+      <c r="GF104" t="inlineStr"/>
+      <c r="GG104" t="inlineStr"/>
+      <c r="GH104" t="inlineStr"/>
+      <c r="GI104" t="inlineStr"/>
+      <c r="GJ104" t="inlineStr"/>
+      <c r="GK104" t="inlineStr"/>
+      <c r="GL104" t="inlineStr"/>
+      <c r="GM104" t="inlineStr"/>
+      <c r="GN104" t="inlineStr"/>
+      <c r="GO104" t="inlineStr"/>
+      <c r="GP104" t="inlineStr"/>
+      <c r="GQ104" t="inlineStr"/>
+      <c r="GR104" t="inlineStr">
+        <is>
+          <t>j1TwYY8F</t>
+        </is>
+      </c>
+      <c r="GS104" t="inlineStr">
+        <is>
+          <t>sonzogni luca</t>
+        </is>
+      </c>
+      <c r="GT104" t="inlineStr"/>
+      <c r="GU104" t="inlineStr"/>
+      <c r="GV104" t="inlineStr"/>
+      <c r="GW104" t="inlineStr"/>
+      <c r="GX104" t="inlineStr"/>
+      <c r="GY104" t="inlineStr"/>
+      <c r="GZ104" t="inlineStr"/>
+      <c r="HA104" t="inlineStr"/>
+      <c r="HB104" t="inlineStr"/>
+      <c r="HC104" t="inlineStr"/>
+      <c r="HD104" t="inlineStr"/>
+      <c r="HE104" t="inlineStr"/>
+      <c r="HF104" t="inlineStr"/>
+      <c r="HG104" t="inlineStr"/>
+      <c r="HH104" t="inlineStr"/>
+      <c r="HI104" t="inlineStr"/>
+      <c r="HJ104" t="inlineStr"/>
+      <c r="HK104" t="inlineStr"/>
+      <c r="HL104" t="inlineStr"/>
+      <c r="HM104" t="inlineStr"/>
+      <c r="HN104" t="inlineStr"/>
+      <c r="HO104" t="inlineStr"/>
+      <c r="HP104" t="inlineStr"/>
+      <c r="HQ104" t="inlineStr"/>
+      <c r="HR104" t="inlineStr"/>
+      <c r="HS104" t="inlineStr"/>
+      <c r="HT104" t="inlineStr"/>
+      <c r="HU104" t="inlineStr"/>
+      <c r="HV104" t="inlineStr"/>
+      <c r="HW104" t="inlineStr"/>
+      <c r="HX104" t="inlineStr"/>
+      <c r="HY104" t="inlineStr"/>
+      <c r="HZ104" t="inlineStr"/>
+      <c r="IA104" t="inlineStr"/>
+      <c r="IB104" t="inlineStr"/>
+      <c r="IC104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>QJM49URT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>bleve marco</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>bmwzhd5k</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>coppolaro mauro</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>GAOlIzwG</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>illanes julian</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>tMqmOicE</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>imperiale marco</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>SEwp6Uhi</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>belloni niccolo</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>dne3gePB</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>schiavi nicolas</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>ddvz0tcQ</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>capezzi leonardo</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>hn4q1pAA</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>cicconi manuel</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>zPp0s4d5</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>panico giuseppe</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>hpPoJ5jN</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>palmieri riccardo</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>dfo0RTSJ</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>capello alessandro</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>8AdgDulS</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>bethers klavs</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>fFGyK9MN</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>curado marcos</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>lELcnVTs</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>quaini alessandro</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>Y1eXtWA3</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>monaco salvatore</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>f71DcoeK</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>bouah devid eugene</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>d8xCwkbI</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>sturaro stefano</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>fRCMv8bK</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>zanellato niccolo</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>GY3wSAqM</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>castellini alessio</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>UZFYMmq1</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>chirico cosimo</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>WCaGAx3g</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>rapisarda francesco</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>M7iZGsW9</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>popovic gabriel</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>prXotgGn</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>cartano raffaele</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>z92952s6</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>cerri leonardo</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Kd5zFbti</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>cherubini luigi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>t8Q8Iav7</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>della latta simone</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>dQK08sbn</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>di matteo tommaso</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>C0IePhv1</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>finotto mattia</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>juFFYgjU</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>grassini davide</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>hrU2YLMp</t>
+        </is>
+      </c>
+      <c r="BI105" t="inlineStr">
+        <is>
+          <t>mazzini stefano</t>
+        </is>
+      </c>
+      <c r="BJ105" t="inlineStr">
+        <is>
+          <t>Ak6MHnNb</t>
+        </is>
+      </c>
+      <c r="BK105" t="inlineStr">
+        <is>
+          <t>motolese mattia</t>
+        </is>
+      </c>
+      <c r="BL105" t="inlineStr">
+        <is>
+          <t>xM8qrrze</t>
+        </is>
+      </c>
+      <c r="BM105" t="inlineStr">
+        <is>
+          <t>oliana filippo</t>
+        </is>
+      </c>
+      <c r="BN105" t="inlineStr">
+        <is>
+          <t>xhitsOAj</t>
+        </is>
+      </c>
+      <c r="BO105" t="inlineStr">
+        <is>
+          <t>palermo ryduan</t>
+        </is>
+      </c>
+      <c r="BP105" t="inlineStr">
+        <is>
+          <t>Ug7hmUUm</t>
+        </is>
+      </c>
+      <c r="BQ105" t="inlineStr">
+        <is>
+          <t>allegra oscar</t>
+        </is>
+      </c>
+      <c r="BR105" t="inlineStr">
+        <is>
+          <t>bVWxGn4d</t>
+        </is>
+      </c>
+      <c r="BS105" t="inlineStr">
+        <is>
+          <t>coriolano alessandro</t>
+        </is>
+      </c>
+      <c r="BT105" t="inlineStr">
+        <is>
+          <t>voxM45Yj</t>
+        </is>
+      </c>
+      <c r="BU105" t="inlineStr">
+        <is>
+          <t>d emilio federico</t>
+        </is>
+      </c>
+      <c r="BV105" t="inlineStr">
+        <is>
+          <t>4lTOMfFA</t>
+        </is>
+      </c>
+      <c r="BW105" t="inlineStr">
+        <is>
+          <t>de luca giuseppe</t>
+        </is>
+      </c>
+      <c r="BX105" t="inlineStr">
+        <is>
+          <t>GzmDcxgr</t>
+        </is>
+      </c>
+      <c r="BY105" t="inlineStr">
+        <is>
+          <t>forti carmelo</t>
+        </is>
+      </c>
+      <c r="BZ105" t="inlineStr">
+        <is>
+          <t>AaIEGLUd</t>
+        </is>
+      </c>
+      <c r="CA105" t="inlineStr">
+        <is>
+          <t>furlan jacopo</t>
+        </is>
+      </c>
+      <c r="CB105" t="inlineStr">
+        <is>
+          <t>tj6tz8eS</t>
+        </is>
+      </c>
+      <c r="CC105" t="inlineStr">
+        <is>
+          <t>nania simone</t>
+        </is>
+      </c>
+      <c r="CD105" t="inlineStr">
+        <is>
+          <t>80jLSPm2</t>
+        </is>
+      </c>
+      <c r="CE105" t="inlineStr">
+        <is>
+          <t>pelleriti marco</t>
+        </is>
+      </c>
+      <c r="CF105" t="inlineStr"/>
+      <c r="CG105" t="inlineStr"/>
+      <c r="CH105" t="inlineStr"/>
+      <c r="CI105" t="inlineStr"/>
+      <c r="CJ105" t="inlineStr"/>
+      <c r="CK105" t="inlineStr"/>
+      <c r="CL105" t="inlineStr"/>
+      <c r="CM105" t="inlineStr"/>
+      <c r="CN105" t="inlineStr"/>
+      <c r="CO105" t="inlineStr"/>
+      <c r="CP105" t="inlineStr">
+        <is>
+          <t>juFFYgjU</t>
+        </is>
+      </c>
+      <c r="CQ105" t="inlineStr">
+        <is>
+          <t>grassini davide</t>
+        </is>
+      </c>
+      <c r="CR105" t="inlineStr">
+        <is>
+          <t>juFFYgjU</t>
+        </is>
+      </c>
+      <c r="CS105" t="inlineStr">
+        <is>
+          <t>grassini davide</t>
+        </is>
+      </c>
+      <c r="CT105" t="inlineStr">
+        <is>
+          <t>SEwp6Uhi</t>
+        </is>
+      </c>
+      <c r="CU105" t="inlineStr">
+        <is>
+          <t>belloni niccolo</t>
+        </is>
+      </c>
+      <c r="CV105" t="inlineStr">
+        <is>
+          <t>Kd5zFbti</t>
+        </is>
+      </c>
+      <c r="CW105" t="inlineStr">
+        <is>
+          <t>cherubini luigi</t>
+        </is>
+      </c>
+      <c r="CX105" t="inlineStr">
+        <is>
+          <t>Kd5zFbti</t>
+        </is>
+      </c>
+      <c r="CY105" t="inlineStr">
+        <is>
+          <t>cherubini luigi</t>
+        </is>
+      </c>
+      <c r="CZ105" t="inlineStr">
+        <is>
+          <t>hpPoJ5jN</t>
+        </is>
+      </c>
+      <c r="DA105" t="inlineStr">
+        <is>
+          <t>palmieri riccardo</t>
+        </is>
+      </c>
+      <c r="DB105" t="inlineStr">
+        <is>
+          <t>t6Pgd1eg</t>
+        </is>
+      </c>
+      <c r="DC105" t="inlineStr">
+        <is>
+          <t>zuelli emanuele</t>
+        </is>
+      </c>
+      <c r="DD105" t="inlineStr">
+        <is>
+          <t>t6Pgd1eg</t>
+        </is>
+      </c>
+      <c r="DE105" t="inlineStr">
+        <is>
+          <t>zuelli emanuele</t>
+        </is>
+      </c>
+      <c r="DF105" t="inlineStr">
+        <is>
+          <t>dne3gePB</t>
+        </is>
+      </c>
+      <c r="DG105" t="inlineStr">
+        <is>
+          <t>schiavi nicolas</t>
+        </is>
+      </c>
+      <c r="DH105" t="inlineStr">
+        <is>
+          <t>xhitsOAj</t>
+        </is>
+      </c>
+      <c r="DI105" t="inlineStr">
+        <is>
+          <t>palermo ryduan</t>
+        </is>
+      </c>
+      <c r="DJ105" t="inlineStr">
+        <is>
+          <t>xhitsOAj</t>
+        </is>
+      </c>
+      <c r="DK105" t="inlineStr">
+        <is>
+          <t>palermo ryduan</t>
+        </is>
+      </c>
+      <c r="DL105" t="inlineStr">
+        <is>
+          <t>zPp0s4d5</t>
+        </is>
+      </c>
+      <c r="DM105" t="inlineStr">
+        <is>
+          <t>panico giuseppe</t>
+        </is>
+      </c>
+      <c r="DN105" t="inlineStr">
+        <is>
+          <t>z92952s6</t>
+        </is>
+      </c>
+      <c r="DO105" t="inlineStr">
+        <is>
+          <t>cerri leonardo</t>
+        </is>
+      </c>
+      <c r="DP105" t="inlineStr">
+        <is>
+          <t>z92952s6</t>
+        </is>
+      </c>
+      <c r="DQ105" t="inlineStr">
+        <is>
+          <t>cerri leonardo</t>
+        </is>
+      </c>
+      <c r="DR105" t="inlineStr">
+        <is>
+          <t>dfo0RTSJ</t>
+        </is>
+      </c>
+      <c r="DS105" t="inlineStr">
+        <is>
+          <t>capello alessandro</t>
+        </is>
+      </c>
+      <c r="DT105" t="inlineStr">
+        <is>
+          <t>GzmDcxgr</t>
+        </is>
+      </c>
+      <c r="DU105" t="inlineStr">
+        <is>
+          <t>forti carmelo</t>
+        </is>
+      </c>
+      <c r="DV105" t="inlineStr">
+        <is>
+          <t>GzmDcxgr</t>
+        </is>
+      </c>
+      <c r="DW105" t="inlineStr">
+        <is>
+          <t>forti carmelo</t>
+        </is>
+      </c>
+      <c r="DX105" t="inlineStr">
+        <is>
+          <t>d8xCwkbI</t>
+        </is>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>sturaro stefano</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>4lTOMfFA</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
+          <t>de luca giuseppe</t>
+        </is>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>4lTOMfFA</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>de luca giuseppe</t>
+        </is>
+      </c>
+      <c r="ED105" t="inlineStr">
+        <is>
+          <t>UZFYMmq1</t>
+        </is>
+      </c>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>chirico cosimo</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr"/>
+      <c r="EG105" t="inlineStr"/>
+      <c r="EH105" t="inlineStr"/>
+      <c r="EI105" t="inlineStr"/>
+      <c r="EJ105" t="inlineStr"/>
+      <c r="EK105" t="inlineStr"/>
+      <c r="EL105" t="inlineStr"/>
+      <c r="EM105" t="inlineStr"/>
+      <c r="EN105" t="inlineStr"/>
+      <c r="EO105" t="inlineStr"/>
+      <c r="EP105" t="inlineStr"/>
+      <c r="EQ105" t="inlineStr"/>
+      <c r="ER105" t="inlineStr"/>
+      <c r="ES105" t="inlineStr"/>
+      <c r="ET105" t="inlineStr"/>
+      <c r="EU105" t="inlineStr"/>
+      <c r="EV105" t="inlineStr"/>
+      <c r="EW105" t="inlineStr"/>
+      <c r="EX105" t="inlineStr"/>
+      <c r="EY105" t="inlineStr"/>
+      <c r="EZ105" t="inlineStr"/>
+      <c r="FA105" t="inlineStr"/>
+      <c r="FB105" t="inlineStr"/>
+      <c r="FC105" t="inlineStr"/>
+      <c r="FD105" t="inlineStr"/>
+      <c r="FE105" t="inlineStr"/>
+      <c r="FF105" t="inlineStr">
+        <is>
+          <t>6c0N7EyD</t>
+        </is>
+      </c>
+      <c r="FG105" t="inlineStr">
+        <is>
+          <t>raimo alessandro</t>
+        </is>
+      </c>
+      <c r="FH105" t="inlineStr">
+        <is>
+          <t>dGs2NgKC</t>
+        </is>
+      </c>
+      <c r="FI105" t="inlineStr">
+        <is>
+          <t>sansaro alessio</t>
+        </is>
+      </c>
+      <c r="FJ105" t="inlineStr"/>
+      <c r="FK105" t="inlineStr"/>
+      <c r="FL105" t="inlineStr"/>
+      <c r="FM105" t="inlineStr"/>
+      <c r="FN105" t="inlineStr"/>
+      <c r="FO105" t="inlineStr"/>
+      <c r="FP105" t="inlineStr">
+        <is>
+          <t>xngA6hD7</t>
+        </is>
+      </c>
+      <c r="FQ105" t="inlineStr">
+        <is>
+          <t>tampucci tomas</t>
+        </is>
+      </c>
+      <c r="FR105" t="inlineStr">
+        <is>
+          <t>t6Pgd1eg</t>
+        </is>
+      </c>
+      <c r="FS105" t="inlineStr">
+        <is>
+          <t>zuelli emanuele</t>
+        </is>
+      </c>
+      <c r="FT105" t="inlineStr"/>
+      <c r="FU105" t="inlineStr"/>
+      <c r="FV105" t="inlineStr"/>
+      <c r="FW105" t="inlineStr"/>
+      <c r="FX105" t="inlineStr"/>
+      <c r="FY105" t="inlineStr"/>
+      <c r="FZ105" t="inlineStr"/>
+      <c r="GA105" t="inlineStr"/>
+      <c r="GB105" t="inlineStr"/>
+      <c r="GC105" t="inlineStr"/>
+      <c r="GD105" t="inlineStr"/>
+      <c r="GE105" t="inlineStr"/>
+      <c r="GF105" t="inlineStr"/>
+      <c r="GG105" t="inlineStr"/>
+      <c r="GH105" t="inlineStr"/>
+      <c r="GI105" t="inlineStr"/>
+      <c r="GJ105" t="inlineStr"/>
+      <c r="GK105" t="inlineStr"/>
+      <c r="GL105" t="inlineStr"/>
+      <c r="GM105" t="inlineStr"/>
+      <c r="GN105" t="inlineStr"/>
+      <c r="GO105" t="inlineStr"/>
+      <c r="GP105" t="inlineStr"/>
+      <c r="GQ105" t="inlineStr"/>
+      <c r="GR105" t="inlineStr"/>
+      <c r="GS105" t="inlineStr"/>
+      <c r="GT105" t="inlineStr"/>
+      <c r="GU105" t="inlineStr"/>
+      <c r="GV105" t="inlineStr"/>
+      <c r="GW105" t="inlineStr"/>
+      <c r="GX105" t="inlineStr"/>
+      <c r="GY105" t="inlineStr"/>
+      <c r="GZ105" t="inlineStr"/>
+      <c r="HA105" t="inlineStr"/>
+      <c r="HB105" t="inlineStr"/>
+      <c r="HC105" t="inlineStr"/>
+      <c r="HD105" t="inlineStr"/>
+      <c r="HE105" t="inlineStr"/>
+      <c r="HF105" t="inlineStr"/>
+      <c r="HG105" t="inlineStr"/>
+      <c r="HH105" t="inlineStr"/>
+      <c r="HI105" t="inlineStr"/>
+      <c r="HJ105" t="inlineStr"/>
+      <c r="HK105" t="inlineStr"/>
+      <c r="HL105" t="inlineStr"/>
+      <c r="HM105" t="inlineStr"/>
+      <c r="HN105" t="inlineStr"/>
+      <c r="HO105" t="inlineStr"/>
+      <c r="HP105" t="inlineStr"/>
+      <c r="HQ105" t="inlineStr"/>
+      <c r="HR105" t="inlineStr"/>
+      <c r="HS105" t="inlineStr"/>
+      <c r="HT105" t="inlineStr"/>
+      <c r="HU105" t="inlineStr"/>
+      <c r="HV105" t="inlineStr"/>
+      <c r="HW105" t="inlineStr"/>
+      <c r="HX105" t="inlineStr"/>
+      <c r="HY105" t="inlineStr"/>
+      <c r="HZ105" t="inlineStr"/>
+      <c r="IA105" t="inlineStr"/>
+      <c r="IB105" t="inlineStr"/>
+      <c r="IC105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
